--- a/01_raw_data/4.1_SOCS/raw/input/D2.5.SVY.AGRI.xlsx
+++ b/01_raw_data/4.1_SOCS/raw/input/D2.5.SVY.AGRI.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/bstacy_worldbank_org/Documents/DECIS/SPI/Data/SPI 2023/01_raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI-Zander/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{945FB191-4DDF-43D9-B6B3-47073DB1BA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF8D53A4-3083-4E10-A9DE-2D16A3812E86}"/>
+  <xr:revisionPtr revIDLastSave="616" documentId="13_ncr:1_{945FB191-4DDF-43D9-B6B3-47073DB1BA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E4486B7-0963-5746-96E6-C7EF60FBF996}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
   </bookViews>
   <sheets>
     <sheet name="2020 DCS" sheetId="16" r:id="rId1"/>
     <sheet name="Data" sheetId="15" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$3:$AG$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$3:$AH$148</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -7072,7 +7072,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7410,9 +7410,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7450,7 +7450,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7556,7 +7556,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7698,7 +7698,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7707,12 +7707,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC45DCA7-689A-4112-94CD-40D7CD7D7038}">
   <dimension ref="A1:AB192"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -10555,7 +10555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>81</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -12533,7 +12533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -12705,7 +12705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -12791,7 +12791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -13049,7 +13049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -13221,7 +13221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>93</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -13823,7 +13823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -13995,7 +13995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>103</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -14253,7 +14253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -14339,7 +14339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -14941,7 +14941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -15199,7 +15199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -15371,7 +15371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:28">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -15457,7 +15457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>119</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -15629,7 +15629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -16059,7 +16059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>131</v>
       </c>
@@ -16575,7 +16575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -16747,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -16833,7 +16833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:28">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -16919,7 +16919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:28">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -17005,7 +17005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -17177,7 +17177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>142</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>143</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -17693,7 +17693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>145</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -17951,7 +17951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -18037,7 +18037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -18209,7 +18209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -18295,7 +18295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -18381,7 +18381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -18467,7 +18467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -18553,7 +18553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -18725,7 +18725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -18811,7 +18811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>158</v>
       </c>
@@ -18897,7 +18897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>159</v>
       </c>
@@ -18983,7 +18983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -19069,7 +19069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>161</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>162</v>
       </c>
@@ -19241,7 +19241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -19327,7 +19327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>164</v>
       </c>
@@ -19413,7 +19413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>165</v>
       </c>
@@ -19499,7 +19499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>166</v>
       </c>
@@ -19585,7 +19585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>167</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>168</v>
       </c>
@@ -19757,7 +19757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
@@ -19843,7 +19843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>170</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>171</v>
       </c>
@@ -20015,7 +20015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>172</v>
       </c>
@@ -20101,7 +20101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>173</v>
       </c>
@@ -20187,7 +20187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -20273,7 +20273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -20359,7 +20359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>176</v>
       </c>
@@ -20445,7 +20445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>177</v>
       </c>
@@ -20531,7 +20531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:28">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>178</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>179</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>180</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>181</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>182</v>
       </c>
@@ -20961,7 +20961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>183</v>
       </c>
@@ -21047,7 +21047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>184</v>
       </c>
@@ -21133,7 +21133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>185</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>186</v>
       </c>
@@ -21305,7 +21305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>187</v>
       </c>
@@ -21391,7 +21391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -21477,7 +21477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>189</v>
       </c>
@@ -21563,7 +21563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>191</v>
       </c>
@@ -21735,7 +21735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>192</v>
       </c>
@@ -21821,7 +21821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:28">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>193</v>
       </c>
@@ -21907,7 +21907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>194</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>195</v>
       </c>
@@ -22079,7 +22079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>196</v>
       </c>
@@ -22165,7 +22165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:28">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>198</v>
       </c>
@@ -22337,7 +22337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -22423,7 +22423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>200</v>
       </c>
@@ -22509,7 +22509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:28">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>201</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -22681,7 +22681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>203</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:28">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>204</v>
       </c>
@@ -22853,7 +22853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:28">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>205</v>
       </c>
@@ -22939,7 +22939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>206</v>
       </c>
@@ -23025,7 +23025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -23111,7 +23111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>208</v>
       </c>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>209</v>
       </c>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>210</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>211</v>
       </c>
@@ -23455,7 +23455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:28">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>212</v>
       </c>
@@ -23541,7 +23541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:28">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>213</v>
       </c>
@@ -23627,7 +23627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:28">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>214</v>
       </c>
@@ -23713,7 +23713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>215</v>
       </c>
@@ -23799,7 +23799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:28">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>216</v>
       </c>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:28">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>217</v>
       </c>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>218</v>
       </c>
@@ -24057,7 +24057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>219</v>
       </c>
@@ -24147,23 +24147,27 @@
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3104A5-0424-4E73-9674-9A43DCFB8F0B}">
-  <dimension ref="A1:BI193"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:BJ193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="9.5703125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="135.5703125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="2" customWidth="1"/>
+    <col min="4" max="5" width="9.5" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="27" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="135.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D1" s="16" t="s">
         <v>220</v>
       </c>
@@ -24173,7 +24177,7 @@
       </c>
       <c r="G1" s="42"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -24259,8 +24263,9 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>222</v>
       </c>
@@ -24357,11 +24362,14 @@
       <c r="AF3" s="48">
         <v>2024</v>
       </c>
-      <c r="AG3" s="42" t="s">
+      <c r="AG3" s="48">
+        <v>2025</v>
+      </c>
+      <c r="AH3" s="42" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -24454,12 +24462,13 @@
       </c>
       <c r="AE4" s="46"/>
       <c r="AF4" s="46"/>
-      <c r="AG4" s="27" t="str">
-        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="27" t="str">
+        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG4=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -24548,12 +24557,13 @@
       <c r="AD5" s="27"/>
       <c r="AE5" s="46"/>
       <c r="AF5" s="46"/>
-      <c r="AG5" s="27" t="str">
-        <f t="shared" ref="AG5:AG68" si="0">+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="27" t="str">
+        <f t="shared" ref="AH5:AH68" si="0">+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG5=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -24642,12 +24652,13 @@
       <c r="AD6" s="27"/>
       <c r="AE6" s="46"/>
       <c r="AF6" s="46"/>
-      <c r="AG6" s="27" t="str">
+      <c r="AG6" s="46"/>
+      <c r="AH6" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -24736,12 +24747,13 @@
       <c r="AD7" s="27"/>
       <c r="AE7" s="46"/>
       <c r="AF7" s="46"/>
-      <c r="AG7" s="27" t="str">
+      <c r="AG7" s="46"/>
+      <c r="AH7" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -24830,12 +24842,13 @@
       <c r="AD8" s="27"/>
       <c r="AE8" s="46"/>
       <c r="AF8" s="46"/>
-      <c r="AG8" s="27" t="str">
+      <c r="AG8" s="46"/>
+      <c r="AH8" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -24924,12 +24937,13 @@
       <c r="AD9" s="27"/>
       <c r="AE9" s="46"/>
       <c r="AF9" s="46"/>
-      <c r="AG9" s="27" t="str">
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2001, 2005, 2007, </v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -25018,12 +25032,13 @@
       <c r="AD10" s="27"/>
       <c r="AE10" s="46"/>
       <c r="AF10" s="46"/>
-      <c r="AG10" s="27" t="str">
+      <c r="AG10" s="46"/>
+      <c r="AH10" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, </v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -25112,12 +25127,13 @@
       <c r="AD11" s="27"/>
       <c r="AE11" s="46"/>
       <c r="AF11" s="46"/>
-      <c r="AG11" s="27" t="str">
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -25206,12 +25222,13 @@
       <c r="AD12" s="27"/>
       <c r="AE12" s="46"/>
       <c r="AF12" s="46"/>
-      <c r="AG12" s="27" t="str">
+      <c r="AG12" s="46"/>
+      <c r="AH12" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -25300,12 +25317,13 @@
       <c r="AD13" s="27"/>
       <c r="AE13" s="46"/>
       <c r="AF13" s="46"/>
-      <c r="AG13" s="27" t="str">
+      <c r="AG13" s="46"/>
+      <c r="AH13" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -25394,12 +25412,13 @@
       <c r="AD14" s="27"/>
       <c r="AE14" s="46"/>
       <c r="AF14" s="46"/>
-      <c r="AG14" s="27" t="str">
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -25488,12 +25507,13 @@
       <c r="AD15" s="27"/>
       <c r="AE15" s="46"/>
       <c r="AF15" s="46"/>
-      <c r="AG15" s="27" t="str">
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -25582,12 +25602,13 @@
       <c r="AD16" s="27"/>
       <c r="AE16" s="46"/>
       <c r="AF16" s="46"/>
-      <c r="AG16" s="27" t="str">
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:61">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -25676,12 +25697,13 @@
       <c r="AD17" s="27"/>
       <c r="AE17" s="46"/>
       <c r="AF17" s="46"/>
-      <c r="AG17" s="27" t="str">
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, 2015, </v>
       </c>
     </row>
-    <row r="18" spans="1:61">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -25770,12 +25792,13 @@
       <c r="AD18" s="27"/>
       <c r="AE18" s="46"/>
       <c r="AF18" s="46"/>
-      <c r="AG18" s="27" t="str">
+      <c r="AG18" s="46"/>
+      <c r="AH18" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:61">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -25864,12 +25887,13 @@
       <c r="AD19" s="27"/>
       <c r="AE19" s="46"/>
       <c r="AF19" s="46"/>
-      <c r="AG19" s="27" t="str">
+      <c r="AG19" s="46"/>
+      <c r="AH19" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2006, 2007, 2009, 2011, 2012, 2013, 2014, 2015, 2017, 2019, </v>
       </c>
     </row>
-    <row r="20" spans="1:61">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -25958,12 +25982,13 @@
       <c r="AD20" s="27"/>
       <c r="AE20" s="46"/>
       <c r="AF20" s="46"/>
-      <c r="AG20" s="27" t="str">
+      <c r="AG20" s="46"/>
+      <c r="AH20" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="21" spans="1:61" s="15" customFormat="1">
+    <row r="21" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -26058,11 +26083,11 @@
         <v>1</v>
       </c>
       <c r="AF21" s="46"/>
-      <c r="AG21" s="27" t="str">
+      <c r="AG21" s="46"/>
+      <c r="AH21" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, 2007, 2013, 2016, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH21"/>
       <c r="AI21"/>
       <c r="AJ21"/>
       <c r="AK21"/>
@@ -26090,8 +26115,9 @@
       <c r="BG21"/>
       <c r="BH21"/>
       <c r="BI21"/>
+      <c r="BJ21"/>
     </row>
-    <row r="22" spans="1:61">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -26180,12 +26206,13 @@
       <c r="AD22" s="27"/>
       <c r="AE22" s="46"/>
       <c r="AF22" s="46"/>
-      <c r="AG22" s="27" t="str">
+      <c r="AG22" s="46"/>
+      <c r="AH22" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, </v>
       </c>
     </row>
-    <row r="23" spans="1:61">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -26274,12 +26301,13 @@
       <c r="AD23" s="27"/>
       <c r="AE23" s="46"/>
       <c r="AF23" s="46"/>
-      <c r="AG23" s="27" t="str">
+      <c r="AG23" s="46"/>
+      <c r="AH23" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2011, </v>
       </c>
     </row>
-    <row r="24" spans="1:61">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -26368,12 +26396,13 @@
       <c r="AD24" s="27"/>
       <c r="AE24" s="46"/>
       <c r="AF24" s="46"/>
-      <c r="AG24" s="27" t="str">
+      <c r="AG24" s="46"/>
+      <c r="AH24" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:61">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -26462,12 +26491,13 @@
       <c r="AD25" s="27"/>
       <c r="AE25" s="46"/>
       <c r="AF25" s="46"/>
-      <c r="AG25" s="27" t="str">
+      <c r="AG25" s="46"/>
+      <c r="AH25" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2019, </v>
       </c>
     </row>
-    <row r="26" spans="1:61">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -26556,12 +26586,13 @@
       <c r="AD26" s="27"/>
       <c r="AE26" s="46"/>
       <c r="AF26" s="46"/>
-      <c r="AG26" s="27" t="str">
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:61">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -26650,12 +26681,13 @@
       <c r="AD27" s="27"/>
       <c r="AE27" s="46"/>
       <c r="AF27" s="46"/>
-      <c r="AG27" s="27" t="str">
+      <c r="AG27" s="46"/>
+      <c r="AH27" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:61">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -26744,12 +26776,13 @@
       <c r="AD28" s="27"/>
       <c r="AE28" s="46"/>
       <c r="AF28" s="46"/>
-      <c r="AG28" s="27" t="str">
+      <c r="AG28" s="46"/>
+      <c r="AH28" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:61">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -26838,12 +26871,13 @@
       <c r="AD29" s="27"/>
       <c r="AE29" s="46"/>
       <c r="AF29" s="46"/>
-      <c r="AG29" s="27" t="str">
+      <c r="AG29" s="46"/>
+      <c r="AH29" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:61">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -26932,12 +26966,13 @@
       <c r="AD30" s="27"/>
       <c r="AE30" s="46"/>
       <c r="AF30" s="46"/>
-      <c r="AG30" s="27" t="str">
+      <c r="AG30" s="46"/>
+      <c r="AH30" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:61">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -27026,12 +27061,13 @@
       <c r="AD31" s="27"/>
       <c r="AE31" s="46"/>
       <c r="AF31" s="46"/>
-      <c r="AG31" s="27" t="str">
+      <c r="AG31" s="46"/>
+      <c r="AH31" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2001, 2008, 2010, 2011, 2013, 2014, 2015, 2016, 2017, 2019, </v>
       </c>
     </row>
-    <row r="32" spans="1:61">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -27120,12 +27156,13 @@
       <c r="AD32" s="27"/>
       <c r="AE32" s="46"/>
       <c r="AF32" s="46"/>
-      <c r="AG32" s="27" t="str">
+      <c r="AG32" s="46"/>
+      <c r="AH32" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -27214,12 +27251,13 @@
       <c r="AD33" s="27"/>
       <c r="AE33" s="46"/>
       <c r="AF33" s="46"/>
-      <c r="AG33" s="27" t="str">
+      <c r="AG33" s="46"/>
+      <c r="AH33" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -27308,12 +27346,13 @@
       <c r="AD34" s="27"/>
       <c r="AE34" s="46"/>
       <c r="AF34" s="46"/>
-      <c r="AG34" s="27" t="str">
+      <c r="AG34" s="46"/>
+      <c r="AH34" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -27402,12 +27441,13 @@
       <c r="AD35" s="27"/>
       <c r="AE35" s="46"/>
       <c r="AF35" s="46"/>
-      <c r="AG35" s="27" t="str">
+      <c r="AG35" s="46"/>
+      <c r="AH35" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -27496,12 +27536,13 @@
       <c r="AD36" s="27"/>
       <c r="AE36" s="46"/>
       <c r="AF36" s="46"/>
-      <c r="AG36" s="27" t="str">
+      <c r="AG36" s="46"/>
+      <c r="AH36" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -27590,12 +27631,13 @@
       <c r="AD37" s="27"/>
       <c r="AE37" s="46"/>
       <c r="AF37" s="46"/>
-      <c r="AG37" s="27" t="str">
+      <c r="AG37" s="46"/>
+      <c r="AH37" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, 2007, 2010, 2013, 2016, 2020, </v>
       </c>
     </row>
-    <row r="38" spans="1:33">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -27684,12 +27726,13 @@
       <c r="AD38" s="27"/>
       <c r="AE38" s="46"/>
       <c r="AF38" s="46"/>
-      <c r="AG38" s="27" t="str">
+      <c r="AG38" s="46"/>
+      <c r="AH38" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -27778,12 +27821,13 @@
       <c r="AD39" s="27"/>
       <c r="AE39" s="46"/>
       <c r="AF39" s="46"/>
-      <c r="AG39" s="27" t="str">
+      <c r="AG39" s="46"/>
+      <c r="AH39" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:33">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -27872,12 +27916,13 @@
       <c r="AD40" s="27"/>
       <c r="AE40" s="46"/>
       <c r="AF40" s="46"/>
-      <c r="AG40" s="27" t="str">
+      <c r="AG40" s="46"/>
+      <c r="AH40" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -27966,12 +28011,13 @@
       <c r="AD41" s="27"/>
       <c r="AE41" s="46"/>
       <c r="AF41" s="46"/>
-      <c r="AG41" s="27" t="str">
+      <c r="AG41" s="46"/>
+      <c r="AH41" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -28060,12 +28106,13 @@
       <c r="AD42" s="27"/>
       <c r="AE42" s="46"/>
       <c r="AF42" s="46"/>
-      <c r="AG42" s="27" t="str">
+      <c r="AG42" s="46"/>
+      <c r="AH42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:33">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -28154,12 +28201,13 @@
       <c r="AD43" s="27"/>
       <c r="AE43" s="46"/>
       <c r="AF43" s="46"/>
-      <c r="AG43" s="27" t="str">
+      <c r="AG43" s="46"/>
+      <c r="AH43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:33">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -28248,12 +28296,13 @@
       <c r="AD44" s="27"/>
       <c r="AE44" s="46"/>
       <c r="AF44" s="46"/>
-      <c r="AG44" s="27" t="str">
+      <c r="AG44" s="46"/>
+      <c r="AH44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:33">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -28342,12 +28391,13 @@
       <c r="AD45" s="27"/>
       <c r="AE45" s="46"/>
       <c r="AF45" s="46"/>
-      <c r="AG45" s="27" t="str">
+      <c r="AG45" s="46"/>
+      <c r="AH45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:33">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -28436,12 +28486,13 @@
       <c r="AD46" s="27"/>
       <c r="AE46" s="46"/>
       <c r="AF46" s="46"/>
-      <c r="AG46" s="27" t="str">
+      <c r="AG46" s="46"/>
+      <c r="AH46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:33">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -28530,12 +28581,13 @@
       <c r="AD47" s="27"/>
       <c r="AE47" s="46"/>
       <c r="AF47" s="46"/>
-      <c r="AG47" s="27" t="str">
+      <c r="AG47" s="46"/>
+      <c r="AH47" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="48" spans="1:33">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -28624,12 +28676,13 @@
       <c r="AD48" s="27"/>
       <c r="AE48" s="46"/>
       <c r="AF48" s="46"/>
-      <c r="AG48" s="27" t="str">
+      <c r="AG48" s="46"/>
+      <c r="AH48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:33">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -28718,12 +28771,13 @@
       <c r="AD49" s="27"/>
       <c r="AE49" s="46"/>
       <c r="AF49" s="46"/>
-      <c r="AG49" s="27" t="str">
+      <c r="AG49" s="46"/>
+      <c r="AH49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:33">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -28812,12 +28866,13 @@
       <c r="AD50" s="27"/>
       <c r="AE50" s="46"/>
       <c r="AF50" s="46"/>
-      <c r="AG50" s="27" t="str">
+      <c r="AG50" s="46"/>
+      <c r="AH50" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="51" spans="1:33">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -28906,12 +28961,13 @@
       <c r="AD51" s="27"/>
       <c r="AE51" s="46"/>
       <c r="AF51" s="46"/>
-      <c r="AG51" s="27" t="str">
+      <c r="AG51" s="46"/>
+      <c r="AH51" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="52" spans="1:33">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -29000,12 +29056,13 @@
       <c r="AD52" s="27"/>
       <c r="AE52" s="46"/>
       <c r="AF52" s="46"/>
-      <c r="AG52" s="27" t="str">
+      <c r="AG52" s="46"/>
+      <c r="AH52" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="53" spans="1:33">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -29094,12 +29151,13 @@
       <c r="AD53" s="27"/>
       <c r="AE53" s="46"/>
       <c r="AF53" s="46"/>
-      <c r="AG53" s="27" t="str">
+      <c r="AG53" s="46"/>
+      <c r="AH53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:33">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -29188,12 +29246,13 @@
       <c r="AD54" s="27"/>
       <c r="AE54" s="46"/>
       <c r="AF54" s="46"/>
-      <c r="AG54" s="27" t="str">
+      <c r="AG54" s="46"/>
+      <c r="AH54" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, 2013, 2014, 2015, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="55" spans="1:33">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -29282,12 +29341,13 @@
       <c r="AD55" s="27"/>
       <c r="AE55" s="46"/>
       <c r="AF55" s="46"/>
-      <c r="AG55" s="27" t="str">
+      <c r="AG55" s="46"/>
+      <c r="AH55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:33">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -29376,12 +29436,13 @@
       <c r="AD56" s="27"/>
       <c r="AE56" s="46"/>
       <c r="AF56" s="46"/>
-      <c r="AG56" s="27" t="str">
+      <c r="AG56" s="46"/>
+      <c r="AH56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:33">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -29470,12 +29531,13 @@
       <c r="AD57" s="27"/>
       <c r="AE57" s="46"/>
       <c r="AF57" s="46"/>
-      <c r="AG57" s="27" t="str">
+      <c r="AG57" s="46"/>
+      <c r="AH57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:33">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -29564,12 +29626,13 @@
       <c r="AD58" s="27"/>
       <c r="AE58" s="46"/>
       <c r="AF58" s="46"/>
-      <c r="AG58" s="27" t="str">
+      <c r="AG58" s="46"/>
+      <c r="AH58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:33">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -29658,12 +29721,13 @@
       <c r="AD59" s="27"/>
       <c r="AE59" s="46"/>
       <c r="AF59" s="46"/>
-      <c r="AG59" s="27" t="str">
+      <c r="AG59" s="46"/>
+      <c r="AH59" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, </v>
       </c>
     </row>
-    <row r="60" spans="1:33">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -29752,12 +29816,13 @@
       <c r="AD60" s="27"/>
       <c r="AE60" s="46"/>
       <c r="AF60" s="46"/>
-      <c r="AG60" s="27" t="str">
+      <c r="AG60" s="46"/>
+      <c r="AH60" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2003, </v>
       </c>
     </row>
-    <row r="61" spans="1:33">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -29846,12 +29911,13 @@
       <c r="AD61" s="27"/>
       <c r="AE61" s="46"/>
       <c r="AF61" s="46"/>
-      <c r="AG61" s="27" t="str">
+      <c r="AG61" s="46"/>
+      <c r="AH61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:33">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -29940,12 +30006,13 @@
       <c r="AD62" s="27"/>
       <c r="AE62" s="46"/>
       <c r="AF62" s="46"/>
-      <c r="AG62" s="27" t="str">
+      <c r="AG62" s="46"/>
+      <c r="AH62" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2018, 2019, </v>
       </c>
     </row>
-    <row r="63" spans="1:33">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -30034,12 +30101,13 @@
       <c r="AD63" s="27"/>
       <c r="AE63" s="46"/>
       <c r="AF63" s="46"/>
-      <c r="AG63" s="27" t="str">
+      <c r="AG63" s="46"/>
+      <c r="AH63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:33">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -30128,12 +30196,13 @@
       <c r="AD64" s="27"/>
       <c r="AE64" s="46"/>
       <c r="AF64" s="46"/>
-      <c r="AG64" s="27" t="str">
+      <c r="AG64" s="46"/>
+      <c r="AH64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:33">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -30222,12 +30291,13 @@
       <c r="AD65" s="27"/>
       <c r="AE65" s="46"/>
       <c r="AF65" s="46"/>
-      <c r="AG65" s="27" t="str">
+      <c r="AG65" s="46"/>
+      <c r="AH65" s="27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="66" spans="1:33">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -30316,12 +30386,13 @@
       <c r="AD66" s="27"/>
       <c r="AE66" s="46"/>
       <c r="AF66" s="46"/>
-      <c r="AG66" s="27" t="str">
+      <c r="AG66" s="46"/>
+      <c r="AH66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:33">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -30410,12 +30481,13 @@
       <c r="AD67" s="27"/>
       <c r="AE67" s="46"/>
       <c r="AF67" s="46"/>
-      <c r="AG67" s="27" t="str">
+      <c r="AG67" s="46"/>
+      <c r="AH67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:33">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -30504,12 +30576,13 @@
       <c r="AD68" s="27"/>
       <c r="AE68" s="46"/>
       <c r="AF68" s="46"/>
-      <c r="AG68" s="27" t="str">
+      <c r="AG68" s="46"/>
+      <c r="AH68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:33">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -30598,12 +30671,13 @@
       <c r="AD69" s="27"/>
       <c r="AE69" s="46"/>
       <c r="AF69" s="46"/>
-      <c r="AG69" s="27" t="str">
-        <f t="shared" ref="AG69:AG132" si="1">+IF($D69=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG69" s="46"/>
+      <c r="AH69" s="27" t="str">
+        <f t="shared" ref="AH69:AH132" si="1">+IF($D69=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG69=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="70" spans="1:33">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -30692,12 +30766,13 @@
       <c r="AD70" s="27"/>
       <c r="AE70" s="46"/>
       <c r="AF70" s="46"/>
-      <c r="AG70" s="27" t="str">
+      <c r="AG70" s="46"/>
+      <c r="AH70" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:33">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -30786,12 +30861,13 @@
       <c r="AD71" s="27"/>
       <c r="AE71" s="46"/>
       <c r="AF71" s="46"/>
-      <c r="AG71" s="27" t="str">
+      <c r="AG71" s="46"/>
+      <c r="AH71" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:33">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -30880,12 +30956,13 @@
       <c r="AD72" s="27"/>
       <c r="AE72" s="46"/>
       <c r="AF72" s="46"/>
-      <c r="AG72" s="27" t="str">
+      <c r="AG72" s="46"/>
+      <c r="AH72" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:33">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -30974,12 +31051,13 @@
       <c r="AD73" s="27"/>
       <c r="AE73" s="46"/>
       <c r="AF73" s="46"/>
-      <c r="AG73" s="27" t="str">
+      <c r="AG73" s="46"/>
+      <c r="AH73" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2009, 2011, 2013, 2014, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="74" spans="1:33">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -31068,12 +31146,13 @@
       <c r="AD74" s="27"/>
       <c r="AE74" s="46"/>
       <c r="AF74" s="46"/>
-      <c r="AG74" s="27" t="str">
+      <c r="AG74" s="46"/>
+      <c r="AH74" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, </v>
       </c>
     </row>
-    <row r="75" spans="1:33">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -31162,12 +31241,13 @@
       <c r="AD75" s="27"/>
       <c r="AE75" s="46"/>
       <c r="AF75" s="46"/>
-      <c r="AG75" s="27" t="str">
+      <c r="AG75" s="46"/>
+      <c r="AH75" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:33">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -31256,12 +31336,13 @@
       <c r="AD76" s="27"/>
       <c r="AE76" s="46"/>
       <c r="AF76" s="46"/>
-      <c r="AG76" s="27" t="str">
+      <c r="AG76" s="46"/>
+      <c r="AH76" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, 2013, 2016, </v>
       </c>
     </row>
-    <row r="77" spans="1:33">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>74</v>
       </c>
@@ -31350,12 +31431,13 @@
       <c r="AD77" s="27"/>
       <c r="AE77" s="46"/>
       <c r="AF77" s="46"/>
-      <c r="AG77" s="27" t="str">
+      <c r="AG77" s="46"/>
+      <c r="AH77" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:33">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>75</v>
       </c>
@@ -31444,12 +31526,13 @@
       <c r="AD78" s="27"/>
       <c r="AE78" s="46"/>
       <c r="AF78" s="46"/>
-      <c r="AG78" s="27" t="str">
+      <c r="AG78" s="46"/>
+      <c r="AH78" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:33">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>76</v>
       </c>
@@ -31538,12 +31621,13 @@
       <c r="AD79" s="27"/>
       <c r="AE79" s="46"/>
       <c r="AF79" s="46"/>
-      <c r="AG79" s="27" t="str">
+      <c r="AG79" s="46"/>
+      <c r="AH79" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:33">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>77</v>
       </c>
@@ -31632,12 +31716,13 @@
       <c r="AD80" s="27"/>
       <c r="AE80" s="46"/>
       <c r="AF80" s="46"/>
-      <c r="AG80" s="27" t="str">
+      <c r="AG80" s="46"/>
+      <c r="AH80" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:33">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>78</v>
       </c>
@@ -31726,12 +31811,13 @@
       <c r="AD81" s="27"/>
       <c r="AE81" s="46"/>
       <c r="AF81" s="46"/>
-      <c r="AG81" s="27" t="str">
+      <c r="AG81" s="46"/>
+      <c r="AH81" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2014, 2017, </v>
       </c>
     </row>
-    <row r="82" spans="1:33">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>79</v>
       </c>
@@ -31820,12 +31906,13 @@
       <c r="AD82" s="27"/>
       <c r="AE82" s="46"/>
       <c r="AF82" s="46"/>
-      <c r="AG82" s="27" t="str">
+      <c r="AG82" s="46"/>
+      <c r="AH82" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:33">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>80</v>
       </c>
@@ -31916,12 +32003,13 @@
         <v>1</v>
       </c>
       <c r="AF83" s="46"/>
-      <c r="AG83" s="27" t="str">
+      <c r="AG83" s="46"/>
+      <c r="AH83" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2023, </v>
       </c>
     </row>
-    <row r="84" spans="1:33">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>81</v>
       </c>
@@ -32010,12 +32098,13 @@
       <c r="AD84" s="27"/>
       <c r="AE84" s="46"/>
       <c r="AF84" s="46"/>
-      <c r="AG84" s="27" t="str">
+      <c r="AG84" s="46"/>
+      <c r="AH84" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="85" spans="1:33">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>82</v>
       </c>
@@ -32104,12 +32193,13 @@
       <c r="AD85" s="27"/>
       <c r="AE85" s="46"/>
       <c r="AF85" s="46"/>
-      <c r="AG85" s="27" t="str">
+      <c r="AG85" s="46"/>
+      <c r="AH85" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2014, 2017, 2019, </v>
       </c>
     </row>
-    <row r="86" spans="1:33">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>83</v>
       </c>
@@ -32198,12 +32288,13 @@
       <c r="AD86" s="27"/>
       <c r="AE86" s="46"/>
       <c r="AF86" s="46"/>
-      <c r="AG86" s="27" t="str">
+      <c r="AG86" s="46"/>
+      <c r="AH86" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:33">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>84</v>
       </c>
@@ -32292,12 +32383,13 @@
       <c r="AD87" s="27"/>
       <c r="AE87" s="46"/>
       <c r="AF87" s="46"/>
-      <c r="AG87" s="27" t="str">
+      <c r="AG87" s="46"/>
+      <c r="AH87" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:33">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>85</v>
       </c>
@@ -32386,12 +32478,13 @@
       <c r="AD88" s="27"/>
       <c r="AE88" s="46"/>
       <c r="AF88" s="46"/>
-      <c r="AG88" s="27" t="str">
+      <c r="AG88" s="46"/>
+      <c r="AH88" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:33">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>86</v>
       </c>
@@ -32480,12 +32573,13 @@
       <c r="AD89" s="27"/>
       <c r="AE89" s="46"/>
       <c r="AF89" s="46"/>
-      <c r="AG89" s="27" t="str">
+      <c r="AG89" s="46"/>
+      <c r="AH89" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="90" spans="1:33">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>87</v>
       </c>
@@ -32574,12 +32668,13 @@
       <c r="AD90" s="27"/>
       <c r="AE90" s="46"/>
       <c r="AF90" s="46"/>
-      <c r="AG90" s="27" t="str">
+      <c r="AG90" s="46"/>
+      <c r="AH90" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:33">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>88</v>
       </c>
@@ -32668,12 +32763,13 @@
       <c r="AD91" s="27"/>
       <c r="AE91" s="46"/>
       <c r="AF91" s="46"/>
-      <c r="AG91" s="27" t="str">
+      <c r="AG91" s="46"/>
+      <c r="AH91" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2006, </v>
       </c>
     </row>
-    <row r="92" spans="1:33">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>89</v>
       </c>
@@ -32762,12 +32858,13 @@
       <c r="AD92" s="27"/>
       <c r="AE92" s="46"/>
       <c r="AF92" s="46"/>
-      <c r="AG92" s="27" t="str">
+      <c r="AG92" s="46"/>
+      <c r="AH92" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:33">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>90</v>
       </c>
@@ -32856,12 +32953,13 @@
       <c r="AD93" s="27"/>
       <c r="AE93" s="46"/>
       <c r="AF93" s="46"/>
-      <c r="AG93" s="27" t="str">
+      <c r="AG93" s="46"/>
+      <c r="AH93" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:33">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>91</v>
       </c>
@@ -32950,12 +33048,13 @@
       <c r="AD94" s="27"/>
       <c r="AE94" s="46"/>
       <c r="AF94" s="46"/>
-      <c r="AG94" s="27" t="str">
+      <c r="AG94" s="46"/>
+      <c r="AH94" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:33">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>92</v>
       </c>
@@ -33044,12 +33143,13 @@
       <c r="AD95" s="27"/>
       <c r="AE95" s="46"/>
       <c r="AF95" s="46"/>
-      <c r="AG95" s="27" t="str">
+      <c r="AG95" s="46"/>
+      <c r="AH95" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:33">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>93</v>
       </c>
@@ -33138,12 +33238,13 @@
       <c r="AD96" s="27"/>
       <c r="AE96" s="46"/>
       <c r="AF96" s="46"/>
-      <c r="AG96" s="27" t="str">
+      <c r="AG96" s="46"/>
+      <c r="AH96" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:33">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <v>94</v>
       </c>
@@ -33232,12 +33333,13 @@
       <c r="AD97" s="27"/>
       <c r="AE97" s="46"/>
       <c r="AF97" s="46"/>
-      <c r="AG97" s="27" t="str">
+      <c r="AG97" s="46"/>
+      <c r="AH97" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2011, 2014, </v>
       </c>
     </row>
-    <row r="98" spans="1:33">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <v>95</v>
       </c>
@@ -33326,12 +33428,13 @@
       <c r="AD98" s="27"/>
       <c r="AE98" s="46"/>
       <c r="AF98" s="46"/>
-      <c r="AG98" s="27" t="str">
+      <c r="AG98" s="46"/>
+      <c r="AH98" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2013, </v>
       </c>
     </row>
-    <row r="99" spans="1:33">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>96</v>
       </c>
@@ -33420,12 +33523,13 @@
       <c r="AD99" s="27"/>
       <c r="AE99" s="46"/>
       <c r="AF99" s="46"/>
-      <c r="AG99" s="27" t="str">
+      <c r="AG99" s="46"/>
+      <c r="AH99" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:33">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>97</v>
       </c>
@@ -33514,12 +33618,13 @@
       <c r="AD100" s="27"/>
       <c r="AE100" s="46"/>
       <c r="AF100" s="46"/>
-      <c r="AG100" s="27" t="str">
+      <c r="AG100" s="46"/>
+      <c r="AH100" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:33">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <v>98</v>
       </c>
@@ -33608,12 +33713,13 @@
       <c r="AD101" s="27"/>
       <c r="AE101" s="46"/>
       <c r="AF101" s="46"/>
-      <c r="AG101" s="27" t="str">
+      <c r="AG101" s="46"/>
+      <c r="AH101" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:33">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <v>99</v>
       </c>
@@ -33702,12 +33808,13 @@
       <c r="AD102" s="27"/>
       <c r="AE102" s="46"/>
       <c r="AF102" s="46"/>
-      <c r="AG102" s="27" t="str">
+      <c r="AG102" s="46"/>
+      <c r="AH102" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:33">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <v>100</v>
       </c>
@@ -33796,12 +33903,13 @@
       <c r="AD103" s="27"/>
       <c r="AE103" s="46"/>
       <c r="AF103" s="46"/>
-      <c r="AG103" s="27" t="str">
+      <c r="AG103" s="46"/>
+      <c r="AH103" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:33">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <v>101</v>
       </c>
@@ -33890,12 +33998,13 @@
       <c r="AD104" s="27"/>
       <c r="AE104" s="46"/>
       <c r="AF104" s="46"/>
-      <c r="AG104" s="27" t="str">
+      <c r="AG104" s="46"/>
+      <c r="AH104" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="105" spans="1:33">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <v>102</v>
       </c>
@@ -33984,12 +34093,13 @@
       <c r="AD105" s="27"/>
       <c r="AE105" s="46"/>
       <c r="AF105" s="46"/>
-      <c r="AG105" s="27" t="str">
+      <c r="AG105" s="46"/>
+      <c r="AH105" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, 2016, 2017, </v>
       </c>
     </row>
-    <row r="106" spans="1:33">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <v>103</v>
       </c>
@@ -34078,12 +34188,13 @@
       <c r="AD106" s="27"/>
       <c r="AE106" s="46"/>
       <c r="AF106" s="46"/>
-      <c r="AG106" s="27" t="str">
+      <c r="AG106" s="46"/>
+      <c r="AH106" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2007, 2013, 2016, 2020, </v>
       </c>
     </row>
-    <row r="107" spans="1:33">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <v>104</v>
       </c>
@@ -34172,12 +34283,13 @@
       <c r="AD107" s="27"/>
       <c r="AE107" s="46"/>
       <c r="AF107" s="46"/>
-      <c r="AG107" s="27" t="str">
+      <c r="AG107" s="46"/>
+      <c r="AH107" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2007, 2013, 2016, </v>
       </c>
     </row>
-    <row r="108" spans="1:33">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <v>105</v>
       </c>
@@ -34266,12 +34378,13 @@
       <c r="AD108" s="27"/>
       <c r="AE108" s="46"/>
       <c r="AF108" s="46"/>
-      <c r="AG108" s="27" t="str">
+      <c r="AG108" s="46"/>
+      <c r="AH108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:33">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <v>106</v>
       </c>
@@ -34360,12 +34473,13 @@
       <c r="AD109" s="44"/>
       <c r="AE109" s="46"/>
       <c r="AF109" s="46"/>
-      <c r="AG109" s="27" t="str">
+      <c r="AG109" s="46"/>
+      <c r="AH109" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2001, 2007, 2008, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="110" spans="1:33">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <v>107</v>
       </c>
@@ -34454,12 +34568,13 @@
       <c r="AD110" s="27"/>
       <c r="AE110" s="46"/>
       <c r="AF110" s="46"/>
-      <c r="AG110" s="27" t="str">
+      <c r="AG110" s="46"/>
+      <c r="AH110" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2015, </v>
       </c>
     </row>
-    <row r="111" spans="1:33">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <v>108</v>
       </c>
@@ -34548,12 +34663,13 @@
       <c r="AD111" s="27"/>
       <c r="AE111" s="46"/>
       <c r="AF111" s="46"/>
-      <c r="AG111" s="27" t="str">
+      <c r="AG111" s="46"/>
+      <c r="AH111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:33">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <v>109</v>
       </c>
@@ -34642,12 +34758,13 @@
       <c r="AD112" s="27"/>
       <c r="AE112" s="46"/>
       <c r="AF112" s="46"/>
-      <c r="AG112" s="27" t="str">
+      <c r="AG112" s="46"/>
+      <c r="AH112" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2006, 2007, 2011, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="113" spans="1:33">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <v>110</v>
       </c>
@@ -34736,12 +34853,13 @@
       <c r="AD113" s="27"/>
       <c r="AE113" s="46"/>
       <c r="AF113" s="46"/>
-      <c r="AG113" s="27" t="str">
+      <c r="AG113" s="46"/>
+      <c r="AH113" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2018, </v>
       </c>
     </row>
-    <row r="114" spans="1:33">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>111</v>
       </c>
@@ -34830,12 +34948,13 @@
       <c r="AD114" s="27"/>
       <c r="AE114" s="46"/>
       <c r="AF114" s="46"/>
-      <c r="AG114" s="27" t="str">
+      <c r="AG114" s="46"/>
+      <c r="AH114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:33">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <v>112</v>
       </c>
@@ -34924,12 +35043,13 @@
       <c r="AD115" s="27"/>
       <c r="AE115" s="46"/>
       <c r="AF115" s="46"/>
-      <c r="AG115" s="27" t="str">
+      <c r="AG115" s="46"/>
+      <c r="AH115" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:33">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <v>113</v>
       </c>
@@ -35018,12 +35138,13 @@
       <c r="AD116" s="27"/>
       <c r="AE116" s="46"/>
       <c r="AF116" s="46"/>
-      <c r="AG116" s="27" t="str">
+      <c r="AG116" s="46"/>
+      <c r="AH116" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:33">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <v>114</v>
       </c>
@@ -35112,12 +35233,13 @@
       <c r="AD117" s="27"/>
       <c r="AE117" s="46"/>
       <c r="AF117" s="46"/>
-      <c r="AG117" s="27" t="str">
+      <c r="AG117" s="46"/>
+      <c r="AH117" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:33">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>115</v>
       </c>
@@ -35206,12 +35328,13 @@
       <c r="AD118" s="27"/>
       <c r="AE118" s="46"/>
       <c r="AF118" s="46"/>
-      <c r="AG118" s="27" t="str">
+      <c r="AG118" s="46"/>
+      <c r="AH118" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, </v>
       </c>
     </row>
-    <row r="119" spans="1:33">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>116</v>
       </c>
@@ -35300,12 +35423,13 @@
       <c r="AD119" s="27"/>
       <c r="AE119" s="46"/>
       <c r="AF119" s="46"/>
-      <c r="AG119" s="27" t="str">
+      <c r="AG119" s="46"/>
+      <c r="AH119" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:33">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <v>117</v>
       </c>
@@ -35394,12 +35518,13 @@
       <c r="AD120" s="27"/>
       <c r="AE120" s="46"/>
       <c r="AF120" s="46"/>
-      <c r="AG120" s="27" t="str">
+      <c r="AG120" s="46"/>
+      <c r="AH120" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="121" spans="1:33">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <v>118</v>
       </c>
@@ -35488,12 +35613,13 @@
       <c r="AD121" s="27"/>
       <c r="AE121" s="46"/>
       <c r="AF121" s="46"/>
-      <c r="AG121" s="27" t="str">
+      <c r="AG121" s="46"/>
+      <c r="AH121" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:33">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>119</v>
       </c>
@@ -35582,12 +35708,13 @@
       <c r="AD122" s="27"/>
       <c r="AE122" s="46"/>
       <c r="AF122" s="46"/>
-      <c r="AG122" s="27" t="str">
+      <c r="AG122" s="46"/>
+      <c r="AH122" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:33">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <v>120</v>
       </c>
@@ -35676,12 +35803,13 @@
       <c r="AD123" s="27"/>
       <c r="AE123" s="46"/>
       <c r="AF123" s="46"/>
-      <c r="AG123" s="27" t="str">
+      <c r="AG123" s="46"/>
+      <c r="AH123" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:33">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>121</v>
       </c>
@@ -35770,12 +35898,13 @@
       <c r="AD124" s="27"/>
       <c r="AE124" s="46"/>
       <c r="AF124" s="46"/>
-      <c r="AG124" s="27" t="str">
+      <c r="AG124" s="46"/>
+      <c r="AH124" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:33">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>122</v>
       </c>
@@ -35864,12 +35993,13 @@
       <c r="AD125" s="27"/>
       <c r="AE125" s="46"/>
       <c r="AF125" s="46"/>
-      <c r="AG125" s="27" t="str">
+      <c r="AG125" s="46"/>
+      <c r="AH125" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:33">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <v>123</v>
       </c>
@@ -35958,12 +36088,13 @@
       <c r="AD126" s="27"/>
       <c r="AE126" s="46"/>
       <c r="AF126" s="46"/>
-      <c r="AG126" s="27" t="str">
+      <c r="AG126" s="46"/>
+      <c r="AH126" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:33">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <v>124</v>
       </c>
@@ -36052,12 +36183,13 @@
       <c r="AD127" s="27"/>
       <c r="AE127" s="46"/>
       <c r="AF127" s="46"/>
-      <c r="AG127" s="27" t="str">
+      <c r="AG127" s="46"/>
+      <c r="AH127" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:33">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <v>125</v>
       </c>
@@ -36146,12 +36278,13 @@
       <c r="AD128" s="27"/>
       <c r="AE128" s="46"/>
       <c r="AF128" s="46"/>
-      <c r="AG128" s="27" t="str">
+      <c r="AG128" s="46"/>
+      <c r="AH128" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2014, 2016, </v>
       </c>
     </row>
-    <row r="129" spans="1:33">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <v>126</v>
       </c>
@@ -36240,12 +36373,13 @@
       <c r="AD129" s="27"/>
       <c r="AE129" s="46"/>
       <c r="AF129" s="46"/>
-      <c r="AG129" s="27" t="str">
+      <c r="AG129" s="46"/>
+      <c r="AH129" s="27" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, </v>
       </c>
     </row>
-    <row r="130" spans="1:33">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <v>127</v>
       </c>
@@ -36334,12 +36468,13 @@
       <c r="AD130" s="27"/>
       <c r="AE130" s="46"/>
       <c r="AF130" s="46"/>
-      <c r="AG130" s="27" t="str">
+      <c r="AG130" s="46"/>
+      <c r="AH130" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="131" spans="1:33">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>128</v>
       </c>
@@ -36428,12 +36563,13 @@
       <c r="AD131" s="27"/>
       <c r="AE131" s="46"/>
       <c r="AF131" s="46"/>
-      <c r="AG131" s="27" t="str">
+      <c r="AG131" s="46"/>
+      <c r="AH131" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:33">
+    <row r="132" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <v>129</v>
       </c>
@@ -36522,12 +36658,13 @@
       <c r="AD132" s="27"/>
       <c r="AE132" s="46"/>
       <c r="AF132" s="46"/>
-      <c r="AG132" s="27" t="str">
+      <c r="AG132" s="46"/>
+      <c r="AH132" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:33">
+    <row r="133" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <v>130</v>
       </c>
@@ -36616,12 +36753,13 @@
       <c r="AD133" s="27"/>
       <c r="AE133" s="46"/>
       <c r="AF133" s="46"/>
-      <c r="AG133" s="27" t="str">
-        <f t="shared" ref="AG133:AG193" si="2">+IF($D133=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG133" s="46"/>
+      <c r="AH133" s="27" t="str">
+        <f t="shared" ref="AH133:AH193" si="2">+IF($D133=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "") &amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "") &amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG133=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:33">
+    <row r="134" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>131</v>
       </c>
@@ -36710,12 +36848,13 @@
       <c r="AD134" s="27"/>
       <c r="AE134" s="46"/>
       <c r="AF134" s="46"/>
-      <c r="AG134" s="27" t="str">
+      <c r="AG134" s="46"/>
+      <c r="AH134" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, </v>
       </c>
     </row>
-    <row r="135" spans="1:33">
+    <row r="135" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>132</v>
       </c>
@@ -36804,12 +36943,13 @@
       <c r="AD135" s="27"/>
       <c r="AE135" s="46"/>
       <c r="AF135" s="46"/>
-      <c r="AG135" s="27" t="str">
+      <c r="AG135" s="46"/>
+      <c r="AH135" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2006, 2016, </v>
       </c>
     </row>
-    <row r="136" spans="1:33">
+    <row r="136" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>133</v>
       </c>
@@ -36898,12 +37038,13 @@
       <c r="AD136" s="27"/>
       <c r="AE136" s="46"/>
       <c r="AF136" s="46"/>
-      <c r="AG136" s="27" t="str">
+      <c r="AG136" s="46"/>
+      <c r="AH136" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:33">
+    <row r="137" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>134</v>
       </c>
@@ -36992,12 +37133,13 @@
       <c r="AD137" s="27"/>
       <c r="AE137" s="46"/>
       <c r="AF137" s="46"/>
-      <c r="AG137" s="27" t="str">
+      <c r="AG137" s="46"/>
+      <c r="AH137" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:33">
+    <row r="138" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>135</v>
       </c>
@@ -37086,12 +37228,13 @@
       <c r="AD138" s="27"/>
       <c r="AE138" s="46"/>
       <c r="AF138" s="46"/>
-      <c r="AG138" s="27" t="str">
+      <c r="AG138" s="46"/>
+      <c r="AH138" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2018, </v>
       </c>
     </row>
-    <row r="139" spans="1:33">
+    <row r="139" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <v>136</v>
       </c>
@@ -37180,12 +37323,13 @@
       <c r="AD139" s="27"/>
       <c r="AE139" s="46"/>
       <c r="AF139" s="46"/>
-      <c r="AG139" s="27" t="str">
+      <c r="AG139" s="46"/>
+      <c r="AH139" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:33">
+    <row r="140" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>137</v>
       </c>
@@ -37274,12 +37418,13 @@
       <c r="AD140" s="27"/>
       <c r="AE140" s="46"/>
       <c r="AF140" s="46"/>
-      <c r="AG140" s="27" t="str">
+      <c r="AG140" s="46"/>
+      <c r="AH140" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:33">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>138</v>
       </c>
@@ -37374,12 +37519,13 @@
         <v>1</v>
       </c>
       <c r="AF141" s="46"/>
-      <c r="AG141" s="27" t="str">
+      <c r="AG141" s="46"/>
+      <c r="AH141" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2021, 2022, 2023, </v>
       </c>
     </row>
-    <row r="142" spans="1:33">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>139</v>
       </c>
@@ -37468,12 +37614,13 @@
       <c r="AD142" s="27"/>
       <c r="AE142" s="46"/>
       <c r="AF142" s="46"/>
-      <c r="AG142" s="27" t="str">
+      <c r="AG142" s="46"/>
+      <c r="AH142" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:33">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>140</v>
       </c>
@@ -37562,12 +37709,13 @@
       <c r="AD143" s="27"/>
       <c r="AE143" s="46"/>
       <c r="AF143" s="46"/>
-      <c r="AG143" s="27" t="str">
+      <c r="AG143" s="46"/>
+      <c r="AH143" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:33">
+    <row r="144" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <v>141</v>
       </c>
@@ -37656,12 +37804,13 @@
       <c r="AD144" s="27"/>
       <c r="AE144" s="46"/>
       <c r="AF144" s="46"/>
-      <c r="AG144" s="27" t="str">
+      <c r="AG144" s="46"/>
+      <c r="AH144" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:36">
+    <row r="145" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <v>142</v>
       </c>
@@ -37750,12 +37899,13 @@
       <c r="AD145" s="27"/>
       <c r="AE145" s="46"/>
       <c r="AF145" s="46"/>
-      <c r="AG145" s="27" t="str">
+      <c r="AG145" s="46"/>
+      <c r="AH145" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:36" ht="15.75" customHeight="1">
+    <row r="146" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>143</v>
       </c>
@@ -37844,12 +37994,13 @@
       <c r="AD146" s="27"/>
       <c r="AE146" s="46"/>
       <c r="AF146" s="46"/>
-      <c r="AG146" s="27" t="str">
+      <c r="AG146" s="46"/>
+      <c r="AH146" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2003, 2007, 2009, 2011, 2012, 2013, 2014, 2015, </v>
       </c>
     </row>
-    <row r="147" spans="1:36">
+    <row r="147" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>144</v>
       </c>
@@ -37938,12 +38089,13 @@
       <c r="AD147" s="27"/>
       <c r="AE147" s="46"/>
       <c r="AF147" s="46"/>
-      <c r="AG147" s="27" t="str">
+      <c r="AG147" s="46"/>
+      <c r="AH147" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2012, 2015, 2017, </v>
       </c>
     </row>
-    <row r="148" spans="1:36">
+    <row r="148" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <v>145</v>
       </c>
@@ -38032,12 +38184,13 @@
       <c r="AD148" s="27"/>
       <c r="AE148" s="46"/>
       <c r="AF148" s="46"/>
-      <c r="AG148" s="27" t="str">
+      <c r="AG148" s="46"/>
+      <c r="AH148" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, 2010, 2015, </v>
       </c>
     </row>
-    <row r="149" spans="1:36">
+    <row r="149" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <v>146</v>
       </c>
@@ -38124,13 +38277,14 @@
       </c>
       <c r="AE149" s="46"/>
       <c r="AF149" s="46"/>
-      <c r="AG149" s="27" t="str">
+      <c r="AG149" s="46"/>
+      <c r="AH149" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH149" s="24"/>
+      <c r="AI149" s="24"/>
     </row>
-    <row r="150" spans="1:36">
+    <row r="150" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <v>147</v>
       </c>
@@ -38217,13 +38371,14 @@
       </c>
       <c r="AE150" s="46"/>
       <c r="AF150" s="46"/>
-      <c r="AG150" s="27" t="str">
+      <c r="AG150" s="46"/>
+      <c r="AH150" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH150" s="24"/>
+      <c r="AI150" s="24"/>
     </row>
-    <row r="151" spans="1:36">
+    <row r="151" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <v>148</v>
       </c>
@@ -38312,15 +38467,16 @@
       <c r="AD151" s="15"/>
       <c r="AE151" s="46"/>
       <c r="AF151" s="46"/>
-      <c r="AG151" s="27" t="str">
+      <c r="AG151" s="46"/>
+      <c r="AH151" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH151" s="47" t="s">
+      <c r="AI151" s="47" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="152" spans="1:36">
+    <row r="152" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <v>149</v>
       </c>
@@ -38407,15 +38563,16 @@
       </c>
       <c r="AE152" s="46"/>
       <c r="AF152" s="46"/>
-      <c r="AG152" s="27" t="str">
+      <c r="AG152" s="46"/>
+      <c r="AH152" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2004, 2006, 2008, 2009, 2010, 2011, 2012, 2014, 2015, 2017, 2018, 2020, </v>
       </c>
-      <c r="AH152" s="35" t="s">
+      <c r="AI152" s="35" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="153" spans="1:36">
+    <row r="153" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <v>150</v>
       </c>
@@ -38502,15 +38659,16 @@
       </c>
       <c r="AE153" s="46"/>
       <c r="AF153" s="46"/>
-      <c r="AG153" s="27" t="str">
+      <c r="AG153" s="46"/>
+      <c r="AH153" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH153" s="35" t="s">
+      <c r="AI153" s="35" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="154" spans="1:36">
+    <row r="154" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <v>151</v>
       </c>
@@ -38597,15 +38755,16 @@
       </c>
       <c r="AE154" s="46"/>
       <c r="AF154" s="46"/>
-      <c r="AG154" s="27" t="str">
+      <c r="AG154" s="46"/>
+      <c r="AH154" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH154" s="36" t="s">
+      <c r="AI154" s="36" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="155" spans="1:36">
+    <row r="155" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <v>152</v>
       </c>
@@ -38692,15 +38851,16 @@
       </c>
       <c r="AE155" s="46"/>
       <c r="AF155" s="46"/>
-      <c r="AG155" s="27" t="str">
+      <c r="AG155" s="46"/>
+      <c r="AH155" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH155" s="35" t="s">
+      <c r="AI155" s="35" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="156" spans="1:36">
+    <row r="156" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <v>153</v>
       </c>
@@ -38787,13 +38947,14 @@
       </c>
       <c r="AE156" s="46"/>
       <c r="AF156" s="46"/>
-      <c r="AG156" s="27" t="str">
+      <c r="AG156" s="46"/>
+      <c r="AH156" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH156" s="24"/>
+      <c r="AI156" s="24"/>
     </row>
-    <row r="157" spans="1:36">
+    <row r="157" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <v>154</v>
       </c>
@@ -38883,15 +39044,16 @@
       </c>
       <c r="AE157" s="46"/>
       <c r="AF157" s="46"/>
-      <c r="AG157" s="27" t="str">
+      <c r="AG157" s="46"/>
+      <c r="AH157" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH157" s="35" t="s">
+      <c r="AI157" s="35" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="158" spans="1:36">
+    <row r="158" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>155</v>
       </c>
@@ -38978,18 +39140,19 @@
       </c>
       <c r="AE158" s="46"/>
       <c r="AF158" s="46"/>
-      <c r="AG158" s="27" t="str">
+      <c r="AG158" s="46"/>
+      <c r="AH158" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH158" s="24" t="s">
+      <c r="AI158" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="AI158" t="s">
+      <c r="AJ158" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="159" spans="1:36">
+    <row r="159" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>156</v>
       </c>
@@ -39078,15 +39241,16 @@
       <c r="AD159" s="45"/>
       <c r="AE159" s="46"/>
       <c r="AF159" s="46"/>
-      <c r="AG159" s="27" t="str">
+      <c r="AG159" s="46"/>
+      <c r="AH159" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH159" s="28"/>
       <c r="AI159" s="28"/>
       <c r="AJ159" s="28"/>
+      <c r="AK159" s="28"/>
     </row>
-    <row r="160" spans="1:36">
+    <row r="160" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>157</v>
       </c>
@@ -39177,15 +39341,16 @@
       </c>
       <c r="AE160" s="46"/>
       <c r="AF160" s="46"/>
-      <c r="AG160" s="27" t="str">
+      <c r="AG160" s="46"/>
+      <c r="AH160" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2022, </v>
       </c>
-      <c r="AH160" s="28"/>
       <c r="AI160" s="28"/>
       <c r="AJ160" s="28"/>
+      <c r="AK160" s="28"/>
     </row>
-    <row r="161" spans="1:38">
+    <row r="161" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>158</v>
       </c>
@@ -39278,24 +39443,25 @@
       </c>
       <c r="AE161" s="46"/>
       <c r="AF161" s="46"/>
-      <c r="AG161" s="27" t="str">
+      <c r="AG161" s="46"/>
+      <c r="AH161" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AH161" s="29" t="s">
+      <c r="AI161" s="29" t="s">
         <v>391</v>
       </c>
-      <c r="AI161" s="29" t="s">
+      <c r="AJ161" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="AJ161" s="29" t="s">
+      <c r="AK161" s="29" t="s">
         <v>393</v>
       </c>
-      <c r="AL161" s="36" t="s">
+      <c r="AM161" s="36" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="162" spans="1:38">
+    <row r="162" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>159</v>
       </c>
@@ -39386,21 +39552,22 @@
       <c r="AF162" s="46">
         <v>1</v>
       </c>
-      <c r="AG162" s="27" t="str">
+      <c r="AG162" s="46"/>
+      <c r="AH162" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1999, 2003, 2005, 2007, 2010, 2013, 2016, 2020, 2024, </v>
       </c>
-      <c r="AH162" s="29" t="s">
+      <c r="AI162" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="AI162" s="29" t="s">
+      <c r="AJ162" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="AJ162" s="28" t="s">
+      <c r="AK162" s="28" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="163" spans="1:38">
+    <row r="163" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>160</v>
       </c>
@@ -39489,21 +39656,22 @@
       <c r="AD163" s="45"/>
       <c r="AE163" s="46"/>
       <c r="AF163" s="46"/>
-      <c r="AG163" s="27" t="str">
+      <c r="AG163" s="46"/>
+      <c r="AH163" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, 2020, </v>
       </c>
-      <c r="AH163" s="30" t="s">
+      <c r="AI163" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="AI163" s="29" t="s">
+      <c r="AJ163" s="29" t="s">
         <v>399</v>
       </c>
-      <c r="AJ163" s="29" t="s">
+      <c r="AK163" s="29" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="164" spans="1:38">
+    <row r="164" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>161</v>
       </c>
@@ -39592,15 +39760,16 @@
       <c r="AD164" s="45"/>
       <c r="AE164" s="46"/>
       <c r="AF164" s="46"/>
-      <c r="AG164" s="27" t="str">
+      <c r="AG164" s="46"/>
+      <c r="AH164" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH164" s="28"/>
       <c r="AI164" s="28"/>
       <c r="AJ164" s="28"/>
+      <c r="AK164" s="28"/>
     </row>
-    <row r="165" spans="1:38">
+    <row r="165" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>162</v>
       </c>
@@ -39689,15 +39858,16 @@
       <c r="AD165" s="45"/>
       <c r="AE165" s="46"/>
       <c r="AF165" s="46"/>
-      <c r="AG165" s="27" t="str">
+      <c r="AG165" s="46"/>
+      <c r="AH165" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH165" s="28"/>
       <c r="AI165" s="28"/>
       <c r="AJ165" s="28"/>
+      <c r="AK165" s="28"/>
     </row>
-    <row r="166" spans="1:38">
+    <row r="166" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>163</v>
       </c>
@@ -39794,19 +39964,20 @@
       <c r="AF166" s="46">
         <v>1</v>
       </c>
-      <c r="AG166" s="27" t="str">
+      <c r="AG166" s="46"/>
+      <c r="AH166" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH166" s="29" t="s">
+      <c r="AI166" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="AI166" s="29" t="s">
+      <c r="AJ166" s="29" t="s">
         <v>405</v>
       </c>
-      <c r="AJ166" s="28"/>
+      <c r="AK166" s="28"/>
     </row>
-    <row r="167" spans="1:38">
+    <row r="167" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>164</v>
       </c>
@@ -39897,24 +40068,25 @@
       <c r="AF167" s="46">
         <v>1</v>
       </c>
-      <c r="AG167" s="27" t="str">
+      <c r="AG167" s="46"/>
+      <c r="AH167" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2024, </v>
       </c>
-      <c r="AH167" s="29" t="s">
+      <c r="AI167" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="AI167" s="29" t="s">
+      <c r="AJ167" s="29" t="s">
         <v>408</v>
       </c>
-      <c r="AJ167" s="28" t="s">
+      <c r="AK167" s="28" t="s">
         <v>409</v>
       </c>
-      <c r="AK167" t="s">
+      <c r="AL167" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="168" spans="1:38">
+    <row r="168" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>165</v>
       </c>
@@ -40005,19 +40177,20 @@
       <c r="AF168" s="46">
         <v>1</v>
       </c>
-      <c r="AG168" s="27" t="str">
+      <c r="AG168" s="46"/>
+      <c r="AH168" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2020, 2024, </v>
       </c>
-      <c r="AH168" s="29" t="s">
+      <c r="AI168" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="AI168" s="29" t="s">
+      <c r="AJ168" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="AJ168" s="28"/>
+      <c r="AK168" s="28"/>
     </row>
-    <row r="169" spans="1:38">
+    <row r="169" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>166</v>
       </c>
@@ -40106,24 +40279,25 @@
       <c r="AD169" s="45"/>
       <c r="AE169" s="46"/>
       <c r="AF169" s="46"/>
-      <c r="AG169" s="27" t="str">
+      <c r="AG169" s="46"/>
+      <c r="AH169" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2020, </v>
       </c>
-      <c r="AH169" s="29" t="s">
+      <c r="AI169" s="29" t="s">
         <v>415</v>
       </c>
-      <c r="AI169" s="29" t="s">
+      <c r="AJ169" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="AJ169" s="29" t="s">
+      <c r="AK169" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="AK169" s="36" t="s">
+      <c r="AL169" s="36" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="170" spans="1:38">
+    <row r="170" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>167</v>
       </c>
@@ -40214,19 +40388,20 @@
       <c r="AF170" s="46">
         <v>1</v>
       </c>
-      <c r="AG170" s="27" t="str">
+      <c r="AG170" s="46"/>
+      <c r="AH170" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2024, </v>
       </c>
-      <c r="AH170" s="29" t="s">
+      <c r="AI170" s="29" t="s">
         <v>420</v>
       </c>
-      <c r="AI170" s="29" t="s">
+      <c r="AJ170" s="29" t="s">
         <v>421</v>
       </c>
-      <c r="AJ170" s="28"/>
+      <c r="AK170" s="28"/>
     </row>
-    <row r="171" spans="1:38">
+    <row r="171" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>168</v>
       </c>
@@ -40315,21 +40490,22 @@
       <c r="AD171" s="45"/>
       <c r="AE171" s="46"/>
       <c r="AF171" s="46"/>
-      <c r="AG171" s="27" t="str">
+      <c r="AG171" s="46"/>
+      <c r="AH171" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH171" s="29" t="s">
+      <c r="AI171" s="29" t="s">
         <v>423</v>
       </c>
-      <c r="AI171" s="29" t="s">
+      <c r="AJ171" s="29" t="s">
         <v>424</v>
       </c>
-      <c r="AJ171" s="29" t="s">
+      <c r="AK171" s="29" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="172" spans="1:38">
+    <row r="172" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>169</v>
       </c>
@@ -40420,21 +40596,22 @@
       <c r="AF172" s="46">
         <v>1</v>
       </c>
-      <c r="AG172" s="27" t="str">
+      <c r="AG172" s="46"/>
+      <c r="AH172" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2024, </v>
       </c>
-      <c r="AH172" s="29" t="s">
+      <c r="AI172" s="29" t="s">
         <v>427</v>
       </c>
-      <c r="AI172" s="29" t="s">
+      <c r="AJ172" s="29" t="s">
         <v>428</v>
       </c>
-      <c r="AJ172" s="29" t="s">
+      <c r="AK172" s="29" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="173" spans="1:38">
+    <row r="173" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>170</v>
       </c>
@@ -40523,19 +40700,20 @@
       <c r="AD173" s="45"/>
       <c r="AE173" s="46"/>
       <c r="AF173" s="46"/>
-      <c r="AG173" s="27" t="str">
+      <c r="AG173" s="46"/>
+      <c r="AH173" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, 2016, 2020, </v>
       </c>
-      <c r="AH173" s="30" t="s">
+      <c r="AI173" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="AI173" s="28" t="s">
+      <c r="AJ173" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="AJ173" s="28"/>
+      <c r="AK173" s="28"/>
     </row>
-    <row r="174" spans="1:38">
+    <row r="174" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>171</v>
       </c>
@@ -40624,17 +40802,18 @@
       <c r="AD174" s="45"/>
       <c r="AE174" s="46"/>
       <c r="AF174" s="46"/>
-      <c r="AG174" s="27" t="str">
+      <c r="AG174" s="46"/>
+      <c r="AH174" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH174" s="29" t="s">
+      <c r="AI174" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="AI174" s="28"/>
       <c r="AJ174" s="28"/>
+      <c r="AK174" s="28"/>
     </row>
-    <row r="175" spans="1:38">
+    <row r="175" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>172</v>
       </c>
@@ -40729,21 +40908,22 @@
       <c r="AF175" s="46">
         <v>1</v>
       </c>
-      <c r="AG175" s="27" t="str">
+      <c r="AG175" s="46"/>
+      <c r="AH175" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2021, 2022, 2024, </v>
       </c>
-      <c r="AH175" s="29" t="s">
+      <c r="AI175" s="29" t="s">
         <v>434</v>
       </c>
-      <c r="AI175" s="29" t="s">
+      <c r="AJ175" s="29" t="s">
         <v>435</v>
       </c>
-      <c r="AJ175" s="28" t="s">
+      <c r="AK175" s="28" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="176" spans="1:38">
+    <row r="176" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>173</v>
       </c>
@@ -40840,24 +41020,25 @@
       <c r="AF176" s="46">
         <v>1</v>
       </c>
-      <c r="AG176" s="27" t="str">
+      <c r="AG176" s="46"/>
+      <c r="AH176" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH176" s="29" t="s">
+      <c r="AI176" s="29" t="s">
         <v>438</v>
       </c>
-      <c r="AI176" s="29" t="s">
+      <c r="AJ176" s="29" t="s">
         <v>439</v>
       </c>
-      <c r="AJ176" s="28" t="s">
+      <c r="AK176" s="28" t="s">
         <v>440</v>
       </c>
-      <c r="AK176" s="36" t="s">
+      <c r="AL176" s="36" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="177" spans="1:36">
+    <row r="177" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <v>174</v>
       </c>
@@ -40946,19 +41127,20 @@
       <c r="AD177" s="45"/>
       <c r="AE177" s="46"/>
       <c r="AF177" s="46"/>
-      <c r="AG177" s="27" t="str">
+      <c r="AG177" s="46"/>
+      <c r="AH177" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, 2016, 2020, </v>
       </c>
-      <c r="AH177" s="29" t="s">
+      <c r="AI177" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="AI177" s="28" t="s">
+      <c r="AJ177" s="28" t="s">
         <v>444</v>
       </c>
-      <c r="AJ177" s="28"/>
+      <c r="AK177" s="28"/>
     </row>
-    <row r="178" spans="1:36">
+    <row r="178" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <v>175</v>
       </c>
@@ -41053,17 +41235,18 @@
         <v>1</v>
       </c>
       <c r="AF178" s="46"/>
-      <c r="AG178" s="27" t="str">
+      <c r="AG178" s="46"/>
+      <c r="AH178" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH178" s="28" t="s">
+      <c r="AI178" s="28" t="s">
         <v>446</v>
       </c>
-      <c r="AI178" s="30"/>
-      <c r="AJ178" s="28"/>
+      <c r="AJ178" s="30"/>
+      <c r="AK178" s="28"/>
     </row>
-    <row r="179" spans="1:36">
+    <row r="179" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <v>176</v>
       </c>
@@ -41152,19 +41335,20 @@
       <c r="AD179" s="45"/>
       <c r="AE179" s="46"/>
       <c r="AF179" s="46"/>
-      <c r="AG179" s="27" t="str">
+      <c r="AG179" s="46"/>
+      <c r="AH179" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH179" s="29" t="s">
+      <c r="AI179" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="AI179" s="28" t="s">
+      <c r="AJ179" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="AJ179" s="28"/>
+      <c r="AK179" s="28"/>
     </row>
-    <row r="180" spans="1:36">
+    <row r="180" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <v>177</v>
       </c>
@@ -41253,17 +41437,18 @@
       <c r="AD180" s="45"/>
       <c r="AE180" s="46"/>
       <c r="AF180" s="46"/>
-      <c r="AG180" s="27" t="str">
+      <c r="AG180" s="46"/>
+      <c r="AH180" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2017, 2018, 2020, </v>
       </c>
-      <c r="AH180" s="28" t="s">
+      <c r="AI180" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="AI180" s="28"/>
       <c r="AJ180" s="28"/>
+      <c r="AK180" s="28"/>
     </row>
-    <row r="181" spans="1:36">
+    <row r="181" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <v>178</v>
       </c>
@@ -41360,19 +41545,20 @@
       <c r="AF181" s="46">
         <v>1</v>
       </c>
-      <c r="AG181" s="27" t="str">
+      <c r="AG181" s="46"/>
+      <c r="AH181" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH181" s="29" t="s">
+      <c r="AI181" s="29" t="s">
         <v>452</v>
       </c>
-      <c r="AI181" s="28" t="s">
+      <c r="AJ181" s="28" t="s">
         <v>453</v>
       </c>
-      <c r="AJ181" s="28"/>
+      <c r="AK181" s="28"/>
     </row>
-    <row r="182" spans="1:36">
+    <row r="182" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>179</v>
       </c>
@@ -41461,17 +41647,18 @@
       <c r="AD182" s="45"/>
       <c r="AE182" s="46"/>
       <c r="AF182" s="46"/>
-      <c r="AG182" s="27" t="str">
+      <c r="AG182" s="46"/>
+      <c r="AH182" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2018, 2019, </v>
       </c>
-      <c r="AH182" s="29" t="s">
+      <c r="AI182" s="29" t="s">
         <v>455</v>
       </c>
-      <c r="AI182" s="28"/>
       <c r="AJ182" s="28"/>
+      <c r="AK182" s="28"/>
     </row>
-    <row r="183" spans="1:36">
+    <row r="183" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>180</v>
       </c>
@@ -41562,15 +41749,16 @@
       <c r="AF183" s="46">
         <v>1</v>
       </c>
-      <c r="AG183" s="27" t="str">
+      <c r="AG183" s="46"/>
+      <c r="AH183" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2020, 2024, </v>
       </c>
-      <c r="AH183" s="28"/>
       <c r="AI183" s="28"/>
       <c r="AJ183" s="28"/>
+      <c r="AK183" s="28"/>
     </row>
-    <row r="184" spans="1:36">
+    <row r="184" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>181</v>
       </c>
@@ -41659,19 +41847,20 @@
       <c r="AD184" s="45"/>
       <c r="AE184" s="46"/>
       <c r="AF184" s="46"/>
-      <c r="AG184" s="27" t="str">
+      <c r="AG184" s="46"/>
+      <c r="AH184" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, </v>
       </c>
-      <c r="AH184" s="28" t="s">
+      <c r="AI184" s="28" t="s">
         <v>458</v>
       </c>
-      <c r="AI184" s="28" t="s">
+      <c r="AJ184" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="AJ184" s="28"/>
+      <c r="AK184" s="28"/>
     </row>
-    <row r="185" spans="1:36">
+    <row r="185" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>182</v>
       </c>
@@ -41762,15 +41951,16 @@
       <c r="AF185" s="46">
         <v>1</v>
       </c>
-      <c r="AG185" s="27" t="str">
+      <c r="AG185" s="46"/>
+      <c r="AH185" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2020, 2024, </v>
       </c>
-      <c r="AH185" s="28"/>
       <c r="AI185" s="28"/>
       <c r="AJ185" s="28"/>
+      <c r="AK185" s="28"/>
     </row>
-    <row r="186" spans="1:36">
+    <row r="186" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>183</v>
       </c>
@@ -41863,19 +42053,20 @@
       <c r="AF186" s="46">
         <v>1</v>
       </c>
-      <c r="AG186" s="27" t="str">
+      <c r="AG186" s="46"/>
+      <c r="AH186" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH186" s="29" t="s">
+      <c r="AI186" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="AI186" s="29" t="s">
+      <c r="AJ186" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="AJ186" s="28"/>
+      <c r="AK186" s="28"/>
     </row>
-    <row r="187" spans="1:36">
+    <row r="187" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>184</v>
       </c>
@@ -41972,19 +42163,22 @@
       <c r="AF187" s="46">
         <v>1</v>
       </c>
-      <c r="AG187" s="27" t="str">
+      <c r="AG187" s="46">
+        <v>1</v>
+      </c>
+      <c r="AH187" s="27" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1999, 2000, 2003, 2004, 2005, 2006, 2008, 2009, 2010, 2011, 2013, 2014, 2015, 2016, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AH187" s="29" t="s">
+        <v xml:space="preserve">1996, 1999, 2000, 2003, 2004, 2005, 2006, 2008, 2009, 2010, 2011, 2013, 2014, 2015, 2016, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AI187" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="AI187" s="29" t="s">
+      <c r="AJ187" s="29" t="s">
         <v>465</v>
       </c>
-      <c r="AJ187" s="28"/>
+      <c r="AK187" s="28"/>
     </row>
-    <row r="188" spans="1:36">
+    <row r="188" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>185</v>
       </c>
@@ -42075,19 +42269,20 @@
       <c r="AF188" s="46">
         <v>1</v>
       </c>
-      <c r="AG188" s="27" t="str">
+      <c r="AG188" s="46"/>
+      <c r="AH188" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 2003, 2005, 2007, 2013, 2016, 2020, 2024, </v>
       </c>
-      <c r="AH188" s="28" t="s">
+      <c r="AI188" s="28" t="s">
         <v>467</v>
       </c>
-      <c r="AI188" s="28" t="s">
+      <c r="AJ188" s="28" t="s">
         <v>468</v>
       </c>
-      <c r="AJ188" s="28"/>
+      <c r="AK188" s="28"/>
     </row>
-    <row r="189" spans="1:36">
+    <row r="189" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>186</v>
       </c>
@@ -42178,15 +42373,16 @@
       <c r="AF189" s="46">
         <v>1</v>
       </c>
-      <c r="AG189" s="27" t="str">
+      <c r="AG189" s="46"/>
+      <c r="AH189" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2024, </v>
       </c>
-      <c r="AH189" s="28"/>
       <c r="AI189" s="28"/>
       <c r="AJ189" s="28"/>
+      <c r="AK189" s="28"/>
     </row>
-    <row r="190" spans="1:36">
+    <row r="190" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A190" s="5">
         <v>187</v>
       </c>
@@ -42283,17 +42479,18 @@
       <c r="AF190" s="46">
         <v>1</v>
       </c>
-      <c r="AG190" s="27" t="str">
+      <c r="AG190" s="46"/>
+      <c r="AH190" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH190" s="28" t="s">
+      <c r="AI190" s="28" t="s">
         <v>471</v>
       </c>
-      <c r="AI190" s="28"/>
       <c r="AJ190" s="28"/>
+      <c r="AK190" s="28"/>
     </row>
-    <row r="191" spans="1:36">
+    <row r="191" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A191" s="5">
         <v>188</v>
       </c>
@@ -42384,17 +42581,18 @@
       <c r="AF191" s="46">
         <v>1</v>
       </c>
-      <c r="AG191" s="27" t="str">
+      <c r="AG191" s="46"/>
+      <c r="AH191" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2007, 2013, 2016, 2020, 2024, </v>
       </c>
-      <c r="AH191" s="28" t="s">
+      <c r="AI191" s="28" t="s">
         <v>473</v>
       </c>
-      <c r="AI191" s="28"/>
       <c r="AJ191" s="28"/>
+      <c r="AK191" s="28"/>
     </row>
-    <row r="192" spans="1:36">
+    <row r="192" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A192" s="5">
         <v>189</v>
       </c>
@@ -42485,17 +42683,18 @@
       <c r="AF192" s="46">
         <v>1</v>
       </c>
-      <c r="AG192" s="27" t="str">
+      <c r="AG192" s="46"/>
+      <c r="AH192" s="27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, 2016, 2020, 2024, </v>
       </c>
-      <c r="AH192" s="29" t="s">
+      <c r="AI192" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="AI192" s="30"/>
       <c r="AJ192" s="30"/>
+      <c r="AK192" s="30"/>
     </row>
-    <row r="193" spans="1:36">
+    <row r="193" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>190</v>
       </c>
@@ -42592,78 +42791,104 @@
       <c r="AF193" s="46">
         <v>1</v>
       </c>
-      <c r="AG193" s="27" t="str">
+      <c r="AG193" s="46">
+        <v>1</v>
+      </c>
+      <c r="AH193" s="27" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AH193" s="29" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AI193" s="29" t="s">
         <v>476</v>
       </c>
-      <c r="AI193" s="29" t="s">
+      <c r="AJ193" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="AJ193" s="28"/>
+      <c r="AK193" s="28"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AI169" r:id="rId1" display="https://www.statistischebibliothek.de/mir/receive/DESerie_mods_00000028" xr:uid="{64074C36-1320-43AE-9C60-6CEAACFA2BA0}"/>
-    <hyperlink ref="AH171" r:id="rId2" xr:uid="{04FF4783-FB0B-4F75-AFA7-7F57A4010060}"/>
-    <hyperlink ref="AH175" r:id="rId3" xr:uid="{36E5813B-847C-48BC-853B-E88A32395847}"/>
-    <hyperlink ref="AH166" r:id="rId4" location="a2" xr:uid="{4B9B6E1D-0A9D-44E4-9FEF-75EBEB7C668F}"/>
-    <hyperlink ref="AH173" r:id="rId5" xr:uid="{57600371-5DA5-4430-986B-C1AD5DD2B758}"/>
-    <hyperlink ref="AH186" r:id="rId6" xr:uid="{DB70C41F-DFD8-4A1A-9749-900A33E766EE}"/>
-    <hyperlink ref="AH187" r:id="rId7" location="/nz.govt.stats/6362a469-f374-412e-ac25-d76fd0962003" xr:uid="{C85DEBE5-5AA3-45EE-9064-99362C4B744E}"/>
-    <hyperlink ref="AH172" r:id="rId8" location="3-Statistical-presentation-2" xr:uid="{EAFD244C-C88C-49C1-95EE-E77635909262}"/>
-    <hyperlink ref="AH161" r:id="rId9" xr:uid="{5947EAC5-C00F-461B-AA48-39E80867D4A2}"/>
-    <hyperlink ref="AH162" r:id="rId10" xr:uid="{7CCE6DD2-8640-48CF-AE43-A1FFA2B5C79B}"/>
-    <hyperlink ref="AH163" r:id="rId11" xr:uid="{7E60D4E2-E073-4C70-8B1E-AFB8678A84F9}"/>
-    <hyperlink ref="AH170" r:id="rId12" xr:uid="{773411CE-A0FF-4196-8F99-AB3E5A55A0C8}"/>
-    <hyperlink ref="AH169" r:id="rId13" xr:uid="{DEDB5A42-D99B-4AF9-9669-546C375F720D}"/>
-    <hyperlink ref="AJ169" r:id="rId14" location="abreadcrumb" xr:uid="{37E0F851-A453-4E88-9363-845512114BD3}"/>
-    <hyperlink ref="AI172" r:id="rId15" location="18-Statistical-processing-17" xr:uid="{EE6616E6-33A5-4676-96A8-76961D9D8DEC}"/>
-    <hyperlink ref="AJ172" r:id="rId16" xr:uid="{82752944-CE6B-41DF-8B5D-8902B604D12B}"/>
-    <hyperlink ref="AH176" r:id="rId17" xr:uid="{CCD52F17-2907-4084-A32A-D9FFFEE88A9B}"/>
-    <hyperlink ref="AH168" r:id="rId18" xr:uid="{45368160-629C-453D-8C86-9AE30AAB3997}"/>
-    <hyperlink ref="AI168" r:id="rId19" xr:uid="{5D3AF745-8F06-4A89-BD79-CD1F6BC2DA03}"/>
-    <hyperlink ref="AH152" r:id="rId20" xr:uid="{0133DC5D-FBFE-421A-8CCB-A1ECB92FA7F0}"/>
-    <hyperlink ref="AH153" r:id="rId21" xr:uid="{A0EBF81D-5BFF-453A-8734-5533B3577157}"/>
-    <hyperlink ref="AH154" r:id="rId22" xr:uid="{E23215D3-D486-402B-B735-1C3B02197972}"/>
-    <hyperlink ref="AH157" r:id="rId23" xr:uid="{BE4294C8-BBE9-4C54-9626-ABD0DF8CAE7A}"/>
-    <hyperlink ref="AI163" r:id="rId24" xr:uid="{B74CB5A0-66DE-4544-829C-FE159F8CBBD8}"/>
-    <hyperlink ref="AI162" r:id="rId25" xr:uid="{6E17708A-BF8B-42B6-A77D-5A0B0026CB61}"/>
-    <hyperlink ref="AH167" r:id="rId26" xr:uid="{0CE3E2BB-9CC0-4BB6-9B85-9A80A481EE01}"/>
-    <hyperlink ref="AI167" r:id="rId27" xr:uid="{DAE03791-F12D-4993-9F51-4DD8B0007E04}"/>
-    <hyperlink ref="AK169" r:id="rId28" xr:uid="{24E4EBAD-ACE5-4C85-9761-1B8E64C2C791}"/>
-    <hyperlink ref="AH174" r:id="rId29" xr:uid="{2208C5FF-F7AB-4181-B4EC-B4BBA9737A3E}"/>
-    <hyperlink ref="AI176" r:id="rId30" xr:uid="{898A8C2F-4E7F-4852-8FB4-65BE558E61E1}"/>
-    <hyperlink ref="AH177" r:id="rId31" xr:uid="{D9B1CDFB-A53E-45F2-98A8-F8D9730074E6}"/>
-    <hyperlink ref="AH179" r:id="rId32" xr:uid="{DB99AEDF-6480-4DB4-8039-FA0C8B9C723A}"/>
-    <hyperlink ref="AH181" r:id="rId33" xr:uid="{DF83BE7F-4F1C-4CB9-9E12-7D07B38A5DDA}"/>
-    <hyperlink ref="AH182" r:id="rId34" xr:uid="{B500CA5F-4492-4F93-B01C-70EFBDD12A6F}"/>
-    <hyperlink ref="AI186" r:id="rId35" xr:uid="{33BF0F16-C844-42E2-BAFE-B565880934F5}"/>
-    <hyperlink ref="AI187" r:id="rId36" xr:uid="{E4E39A4C-71C1-493C-B9A9-47C98F9CAED5}"/>
-    <hyperlink ref="AH193" r:id="rId37" xr:uid="{FD39834B-170E-49C6-B11D-9B0850FCAFED}"/>
-    <hyperlink ref="AI193" r:id="rId38" xr:uid="{6B4FD5B1-5068-4B3F-B331-9199373ABBFF}"/>
-    <hyperlink ref="AH151" r:id="rId39" xr:uid="{611436FD-D021-483E-8AC5-03E78F7001EF}"/>
-    <hyperlink ref="AH192" r:id="rId40" xr:uid="{7505B978-54EB-49B9-8332-8ADEF37D11DB}"/>
-    <hyperlink ref="AH155" r:id="rId41" xr:uid="{99EE260C-E967-410E-8999-C67A9188A5F9}"/>
-    <hyperlink ref="AI161" r:id="rId42" xr:uid="{3EBE222D-03E1-478F-A96F-5F5AB1924C6A}"/>
-    <hyperlink ref="AJ161" r:id="rId43" xr:uid="{15EA527C-848F-42BF-87A6-D938CAFA24B2}"/>
-    <hyperlink ref="AL161" r:id="rId44" xr:uid="{D64FCDE3-E51D-454F-9F08-0D820D5C6D7D}"/>
-    <hyperlink ref="AJ163" r:id="rId45" xr:uid="{BC96C27E-7B71-4F36-A362-843C90263C4C}"/>
-    <hyperlink ref="AI166" r:id="rId46" xr:uid="{3A23ABD2-6957-4604-BE28-A93EE0BFC6FA}"/>
-    <hyperlink ref="AI170" r:id="rId47" xr:uid="{477DB110-C843-4EFC-B028-6AD16A59E7EE}"/>
-    <hyperlink ref="AI171" r:id="rId48" xr:uid="{8B3C149A-0B50-4B22-A2FF-68971E2C500D}"/>
-    <hyperlink ref="AJ171" r:id="rId49" xr:uid="{674E1B0A-8A7E-4384-8F1F-DEB853F7D991}"/>
-    <hyperlink ref="AK176" r:id="rId50" xr:uid="{09E65C4F-E0D3-4BC0-9FBB-8D7A38937092}"/>
+    <hyperlink ref="AJ169" r:id="rId1" display="https://www.statistischebibliothek.de/mir/receive/DESerie_mods_00000028" xr:uid="{64074C36-1320-43AE-9C60-6CEAACFA2BA0}"/>
+    <hyperlink ref="AI171" r:id="rId2" xr:uid="{04FF4783-FB0B-4F75-AFA7-7F57A4010060}"/>
+    <hyperlink ref="AI175" r:id="rId3" xr:uid="{36E5813B-847C-48BC-853B-E88A32395847}"/>
+    <hyperlink ref="AI166" r:id="rId4" location="a2" xr:uid="{4B9B6E1D-0A9D-44E4-9FEF-75EBEB7C668F}"/>
+    <hyperlink ref="AI173" r:id="rId5" xr:uid="{57600371-5DA5-4430-986B-C1AD5DD2B758}"/>
+    <hyperlink ref="AI186" r:id="rId6" xr:uid="{DB70C41F-DFD8-4A1A-9749-900A33E766EE}"/>
+    <hyperlink ref="AI187" r:id="rId7" location="/nz.govt.stats/6362a469-f374-412e-ac25-d76fd0962003" xr:uid="{C85DEBE5-5AA3-45EE-9064-99362C4B744E}"/>
+    <hyperlink ref="AI172" r:id="rId8" location="3-Statistical-presentation-2" xr:uid="{EAFD244C-C88C-49C1-95EE-E77635909262}"/>
+    <hyperlink ref="AI161" r:id="rId9" xr:uid="{5947EAC5-C00F-461B-AA48-39E80867D4A2}"/>
+    <hyperlink ref="AI162" r:id="rId10" xr:uid="{7CCE6DD2-8640-48CF-AE43-A1FFA2B5C79B}"/>
+    <hyperlink ref="AI163" r:id="rId11" xr:uid="{7E60D4E2-E073-4C70-8B1E-AFB8678A84F9}"/>
+    <hyperlink ref="AI170" r:id="rId12" xr:uid="{773411CE-A0FF-4196-8F99-AB3E5A55A0C8}"/>
+    <hyperlink ref="AI169" r:id="rId13" xr:uid="{DEDB5A42-D99B-4AF9-9669-546C375F720D}"/>
+    <hyperlink ref="AK169" r:id="rId14" location="abreadcrumb" xr:uid="{37E0F851-A453-4E88-9363-845512114BD3}"/>
+    <hyperlink ref="AJ172" r:id="rId15" location="18-Statistical-processing-17" xr:uid="{EE6616E6-33A5-4676-96A8-76961D9D8DEC}"/>
+    <hyperlink ref="AK172" r:id="rId16" xr:uid="{82752944-CE6B-41DF-8B5D-8902B604D12B}"/>
+    <hyperlink ref="AI176" r:id="rId17" xr:uid="{CCD52F17-2907-4084-A32A-D9FFFEE88A9B}"/>
+    <hyperlink ref="AI168" r:id="rId18" xr:uid="{45368160-629C-453D-8C86-9AE30AAB3997}"/>
+    <hyperlink ref="AJ168" r:id="rId19" xr:uid="{5D3AF745-8F06-4A89-BD79-CD1F6BC2DA03}"/>
+    <hyperlink ref="AI152" r:id="rId20" xr:uid="{0133DC5D-FBFE-421A-8CCB-A1ECB92FA7F0}"/>
+    <hyperlink ref="AI153" r:id="rId21" xr:uid="{A0EBF81D-5BFF-453A-8734-5533B3577157}"/>
+    <hyperlink ref="AI154" r:id="rId22" xr:uid="{E23215D3-D486-402B-B735-1C3B02197972}"/>
+    <hyperlink ref="AI157" r:id="rId23" xr:uid="{BE4294C8-BBE9-4C54-9626-ABD0DF8CAE7A}"/>
+    <hyperlink ref="AJ163" r:id="rId24" xr:uid="{B74CB5A0-66DE-4544-829C-FE159F8CBBD8}"/>
+    <hyperlink ref="AJ162" r:id="rId25" xr:uid="{6E17708A-BF8B-42B6-A77D-5A0B0026CB61}"/>
+    <hyperlink ref="AI167" r:id="rId26" xr:uid="{0CE3E2BB-9CC0-4BB6-9B85-9A80A481EE01}"/>
+    <hyperlink ref="AJ167" r:id="rId27" xr:uid="{DAE03791-F12D-4993-9F51-4DD8B0007E04}"/>
+    <hyperlink ref="AL169" r:id="rId28" xr:uid="{24E4EBAD-ACE5-4C85-9761-1B8E64C2C791}"/>
+    <hyperlink ref="AI174" r:id="rId29" xr:uid="{2208C5FF-F7AB-4181-B4EC-B4BBA9737A3E}"/>
+    <hyperlink ref="AJ176" r:id="rId30" xr:uid="{898A8C2F-4E7F-4852-8FB4-65BE558E61E1}"/>
+    <hyperlink ref="AI177" r:id="rId31" xr:uid="{D9B1CDFB-A53E-45F2-98A8-F8D9730074E6}"/>
+    <hyperlink ref="AI179" r:id="rId32" xr:uid="{DB99AEDF-6480-4DB4-8039-FA0C8B9C723A}"/>
+    <hyperlink ref="AI181" r:id="rId33" xr:uid="{DF83BE7F-4F1C-4CB9-9E12-7D07B38A5DDA}"/>
+    <hyperlink ref="AI182" r:id="rId34" xr:uid="{B500CA5F-4492-4F93-B01C-70EFBDD12A6F}"/>
+    <hyperlink ref="AJ186" r:id="rId35" xr:uid="{33BF0F16-C844-42E2-BAFE-B565880934F5}"/>
+    <hyperlink ref="AJ187" r:id="rId36" xr:uid="{E4E39A4C-71C1-493C-B9A9-47C98F9CAED5}"/>
+    <hyperlink ref="AI193" r:id="rId37" xr:uid="{FD39834B-170E-49C6-B11D-9B0850FCAFED}"/>
+    <hyperlink ref="AJ193" r:id="rId38" xr:uid="{6B4FD5B1-5068-4B3F-B331-9199373ABBFF}"/>
+    <hyperlink ref="AI151" r:id="rId39" xr:uid="{611436FD-D021-483E-8AC5-03E78F7001EF}"/>
+    <hyperlink ref="AI192" r:id="rId40" xr:uid="{7505B978-54EB-49B9-8332-8ADEF37D11DB}"/>
+    <hyperlink ref="AI155" r:id="rId41" xr:uid="{99EE260C-E967-410E-8999-C67A9188A5F9}"/>
+    <hyperlink ref="AJ161" r:id="rId42" xr:uid="{3EBE222D-03E1-478F-A96F-5F5AB1924C6A}"/>
+    <hyperlink ref="AK161" r:id="rId43" xr:uid="{15EA527C-848F-42BF-87A6-D938CAFA24B2}"/>
+    <hyperlink ref="AM161" r:id="rId44" xr:uid="{D64FCDE3-E51D-454F-9F08-0D820D5C6D7D}"/>
+    <hyperlink ref="AK163" r:id="rId45" xr:uid="{BC96C27E-7B71-4F36-A362-843C90263C4C}"/>
+    <hyperlink ref="AJ166" r:id="rId46" xr:uid="{3A23ABD2-6957-4604-BE28-A93EE0BFC6FA}"/>
+    <hyperlink ref="AJ170" r:id="rId47" xr:uid="{477DB110-C843-4EFC-B028-6AD16A59E7EE}"/>
+    <hyperlink ref="AJ171" r:id="rId48" xr:uid="{8B3C149A-0B50-4B22-A2FF-68971E2C500D}"/>
+    <hyperlink ref="AK171" r:id="rId49" xr:uid="{674E1B0A-8A7E-4384-8F1F-DEB853F7D991}"/>
+    <hyperlink ref="AL176" r:id="rId50" xr:uid="{09E65C4F-E0D3-4BC0-9FBB-8D7A38937092}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId51"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId52"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ADB9CD767C4FF34281D6635032C5B89D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b7ad1acb7d07f4c67b79ea712f2c443">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b19ad29f-88fa-4d62-ac16-34b992563bf9" xmlns:ns3="e781ea9d-1795-4792-8d8d-c86ae526af93" xmlns:ns4="3e02667f-0271-471b-bd6e-11a2e16def1d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0bd56705adf4bb69ae57d53dbdc9cd2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
@@ -42911,34 +43136,48 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B199E69-5DD2-46D3-99E7-CEF1DD03AE5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACEEE91F-8CDF-4F2C-85D3-58EC881B6941}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACEEE91F-8CDF-4F2C-85D3-58EC881B6941}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B199E69-5DD2-46D3-99E7-CEF1DD03AE5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>